--- a/LastFPS/Excel/Hub.xlsx
+++ b/LastFPS/Excel/Hub.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_README" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,42 +15,68 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DT_RadioTransmission" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DT_QuestData'!$A$1:$V$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DT_QuestData'!$A$1:$X$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'DT_NPCData'!$A$1:$F$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DT_DialogueData'!$A$1:$C$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'DT_ItemData'!$A$1:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'DT_ItemData'!$A$1:$I$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'DT_ShopData'!$A$1:$G$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'DT_RadioTransmission'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'DT_RadioTransmission'!$A$1:$G$16</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -60,12 +85,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00203864"/>
+        <fgColor rgb="FF203864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF203864"/>
       </patternFill>
     </fill>
   </fills>
@@ -81,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -92,9 +122,12 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -458,19 +491,19 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="110" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20.25" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>엑셀 데이터 편집 규칙</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr"/>
+      <c r="B1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -579,8 +612,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:Y13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="80" customWidth="1" min="2" max="2"/>
@@ -592,7 +625,7 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="80" customWidth="1" min="10" max="10"/>
-    <col width="80" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
     <col width="80" customWidth="1" min="12" max="12"/>
     <col width="23" customWidth="1" min="13" max="13"/>
     <col width="24" customWidth="1" min="14" max="14"/>
@@ -604,6 +637,7 @@
     <col width="13" customWidth="1" min="20" max="20"/>
     <col width="15" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="21.375" bestFit="1" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -659,62 +693,77 @@
       </c>
       <c r="K1" s="5" t="inlineStr">
         <is>
+          <t>NPCButtonTextKey</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>Objectives</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>bSequentialObjectives</t>
         </is>
       </c>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="O1" s="5" t="inlineStr">
         <is>
           <t>RadioOnStart</t>
         </is>
       </c>
-      <c r="O1" s="5" t="inlineStr">
+      <c r="P1" s="5" t="inlineStr">
         <is>
           <t>RadioOnComplete</t>
         </is>
       </c>
-      <c r="P1" s="5" t="inlineStr">
+      <c r="Q1" s="6" t="inlineStr">
+        <is>
+          <t>CinematicOnStart</t>
+        </is>
+      </c>
+      <c r="R1" s="5" t="inlineStr">
         <is>
           <t>Reward</t>
         </is>
       </c>
-      <c r="Q1" s="5" t="inlineStr">
+      <c r="S1" s="5" t="inlineStr">
         <is>
           <t>RewardText</t>
         </is>
       </c>
-      <c r="R1" s="5" t="inlineStr">
+      <c r="T1" s="5" t="inlineStr">
         <is>
           <t>Icon</t>
         </is>
       </c>
-      <c r="S1" s="5" t="inlineStr">
+      <c r="U1" s="5" t="inlineStr">
         <is>
           <t>PrereqQuestId</t>
         </is>
       </c>
-      <c r="T1" s="5" t="inlineStr">
+      <c r="V1" s="5" t="inlineStr">
         <is>
           <t>NextQuestId</t>
         </is>
       </c>
-      <c r="U1" s="5" t="inlineStr">
+      <c r="W1" s="5" t="inlineStr">
         <is>
           <t>QuestGiverNPC</t>
         </is>
       </c>
-      <c r="V1" s="5" t="inlineStr">
+      <c r="X1" s="5" t="inlineStr">
         <is>
           <t>bAutoClaim</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>bRepeatable</t>
         </is>
       </c>
     </row>
@@ -726,7 +775,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "1AF40C234842CCE1DF2FF78A25EE8D39", "귀환 보급")</t>
+          <t>NSLOCTEXT("", "A08171B442FE41EDBEC3D189E477FED5", "귀환 신고")</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -734,9 +783,16 @@
           <t>Main</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("", "BDBDC9E34BABBE15CF3ED6AC588A2FD8", "기지 적응")</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("", "2F245EE34DF428D8BD47EE9B1C93470F", "Chapter 1: 재정비")</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>1</t>
@@ -754,40 +810,52 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "3106BC5D45D86532B87E459FD98C5E11", "전초기지에서 귀환 보급을 수령한다.")</t>
+          <t>NSLOCTEXT("", "0997A9204F1F5C9A3A0EE79101216A41", "교육 조교 탈에게 복귀를 신고하고 보급을 수령한다.")</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "B825127E43C41D6D0A6D0FA9D2906C28", "전선 복귀를 앞둔 작전원에게 지급되는 기본 보급. 별도 조건 없이 보급 창구에서 즉시 수령할 수 있다.")</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>Quest.NPCButton.Q_Welcome</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("", "848A5C0E4007EF2ECD87C1863F930CAD", "전선에서 복귀한 계승자는 교육 조교에게 복귀 신고를 마친 뒤 보급 창구에 들러야 한다. 서류상 아직 실종자로 남아 있으니 절차부터 밟아라.")</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+          <t>((Type=TalkToNPC,TargetId="NPC_Instructor",TargetTag=(TagName=""),GuidanceNPCRowName="",GuidanceScreenTag=(TagName=""),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("", "A2311E5A4AD8852D9D58B5971D0D0EEF", "교육 조교 탈에게 복귀 신고"),RadioOnStart=,RadioOnComplete=("Radio_Welcome_Start")),(Type=TalkToNPC,TargetId="NPC_ItemShop",TargetTag=(TagName=""),GuidanceNPCRowName="",GuidanceScreenTag=(TagName=""),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("", "980BFF964F60BD6A86F9C0862045085A", "보급상 데크에게 보급 수령"),RadioOnStart=,RadioOnComplete=))</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>("Radio_Base_Welcome")</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>(Credits=500,Items=((RowId="Cons_Repair_01",Count=2)))</t>
+          <t>("Radio_Welcome_Clear")</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "04103FCF4CCDF9E1538ADC8E8CDFCF1C", "크레딧 500 · 나노 수리킷 ×2")</t>
+          <t>(Sequence=None,RequiredWorld=None,StartDelay=0.000000,PlayRate=1.000000,bHideHUD=True,bHidePlayer=True,bDisableMovementInput=True,bDisableLookAtInput=True,bSkippable=True)</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>(Credits=500,PurchaseRefund=(Rate=0.000000,MaxCredits=0),Items=((RowId="Cons_Repair_01",Count=2)))</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>NSLOCTEXT("", "E5B2066C4E434B056CA60DAF9EF72BC2", "크레딧 500 · 나노 수리킷 ×2")</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -801,6 +869,21 @@
         </is>
       </c>
       <c r="V2" t="inlineStr">
+        <is>
+          <t>Q_Mobility</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>NPC_Instructor</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -814,17 +897,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "5E51555144423AC68FCAB48EE8F35CCA", "기동 규격 확보")</t>
+          <t>NSLOCTEXT("", "39BA261F4AD6888ACE28BC8E17D5B8E4", "기동 규격 확보")</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Side</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("", "FF499A4F4637BC283C696A84D75A4D9F", "기지 적응")</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("", "7EF427CB499F7106A986AF9397EAD1EB", "Chapter 1: 재정비")</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>1</t>
@@ -837,49 +927,57 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>InProgress</t>
+          <t>NotStarted</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "E5153E4947ABABB8BCCAE9A32E1575EC", "질풍 모듈을 확보해 기동 규격을 맞춘다.")</t>
+          <t>NSLOCTEXT("", "86C46A5141FCA986CE045EA1A644FD6C", "질풍 모듈을 구해 세라에게 장착을 맡긴다.")</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "5A2BCC8540544085E5D5DCBB63B8D9FE", "차기 작전은 고속 강습 위주로 편성된다. 상점에서 질풍 모듈을 조달해 외골격 기동 규격을 충족시켜라.")</t>
+          <t>Quest.NPCButton.Q_Mobility</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>((Type=AcquireItem,TargetId="Mod_Swift_01",TargetTag=(TagName=""),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "9E73F58742248D17340256AE511A3224", "질풍 모듈 확보"),RadioOnStart=,RadioOnComplete=))</t>
+          <t>NSLOCTEXT("", "EAEA43B54408EE75C8D2868617F6E2E0", "차기 작전은 고속 강습 위주로 편성된다. 보급상 데크에게서 질풍 모듈을 구매한 뒤, 모듈 관리관 세라에게 가져가 외골격에 체결하라.")</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+          <t>((Type=AcquireItem,TargetId="Mod_Swift_01",TargetTag=(TagName=""),GuidanceNPCRowName="NPC_ItemShop",GuidanceScreenTag=(TagName="UI.Screen.Shop"),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("", "2A3FC29140B33E566049A3A658B1463E", "보급상 데크에게서 질풍 모듈 구매"),RadioOnStart=,RadioOnComplete=),(Type=TalkToNPC,TargetId="NPC_ModuleManager",TargetTag=(TagName=""),GuidanceNPCRowName="",GuidanceScreenTag=(TagName=""),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("", "0A3E2B26459D926181B6C28B7113A04F", "세라에게 장착 요청"),RadioOnStart=,RadioOnComplete=))</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>("Radio_Mobility_Start")</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>(Credits=1200,Items=)</t>
+          <t>("Radio_Mobility_Clear")</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "7A8920044FE16AD5027066B2E9C62412", "크레딧 1,200")</t>
+          <t>(Sequence="/Game/Cinematics/Quest/Q_Mobility/LS_Q_Mobility_Start.LS_Q_Mobility_Start",RequiredWorld="/Game/Maps/IngameMap/HubMap1.HubMap1",StartDelay=0.350000,PlayRate=1.000000,bHideHUD=True,bHidePlayer=True,bDisableMovementInput=True,bDisableLookAtInput=True,bSkippable=True)</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>(Credits=300,PurchaseRefund=(Rate=1.000000,MaxCredits=0),Items=)</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>NSLOCTEXT("", "B64F30EF4FF3E8012EEDF5B98C59A432", "구매액 100% 환급 · 완료 보너스 300 크레딧")</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -889,10 +987,25 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Q_Welcome</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
+        <is>
+          <t>Q_Endurance</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>NPC_ModuleManager</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -906,20 +1019,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "E161F70449232A6E0C0AC5B51285BFC5", "지구력 보강")</t>
+          <t>NSLOCTEXT("", "CFA2C4CF4C797A0F725D979243BCC962", "지구력 보강")</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Side</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("", "5312EE36496793D24C61B2A545C53B22", "기지 적응")</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("", "16A730204B3B93125380E5A2174A0DCD", "Chapter 1: 재정비")</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -929,49 +1049,57 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>InProgress</t>
+          <t>NotStarted</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "FADA6B8D47DF2DD8F282878264AEA59C", "지구력 코어를 조달해 장기 작전에 대비한다.")</t>
+          <t>NSLOCTEXT("", "8AB8A3944573E42CA3BC159AA3CBC1A2", "지구력 코어를 구해 보로스에게 정비를 맡긴다.")</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "74298B1A42635920ADB2B99E21F5BE26", "장기 침투 작전에는 안정적인 에너지 순환이 필수다. 지구력 코어를 확보해 스태미나 규격을 보강하라.")</t>
+          <t>Quest.NPCButton.Q_Endurance</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>((Type=AcquireItem,TargetId="Mod_Endure_01",TargetTag=(TagName=""),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "B52E3B5C48A9C43F16325C8283B23A23", "지구력 코어 확보"),RadioOnStart=,RadioOnComplete=))</t>
+          <t>NSLOCTEXT("", "E4B70F55445E431B710BF9BE9F0948A1", "장기 침투 작전에는 안정적인 에너지 순환이 필수다. 보급상 데크에게서 지구력 코어를 구매한 뒤 정비병 보로스에게 가져가라.")</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+          <t>((Type=AcquireItem,TargetId="Mod_Endure_01",TargetTag=(TagName=""),GuidanceNPCRowName="NPC_ItemShop",GuidanceScreenTag=(TagName="UI.Screen.Shop"),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("", "022C6CCA4B044CBB35EC3C8FBDD465D7", "보급상 데크에게서 지구력 코어 구매"),RadioOnStart=,RadioOnComplete=),(Type=TalkToNPC,TargetId="NPC_Mechanic",TargetTag=(TagName=""),GuidanceNPCRowName="",GuidanceScreenTag=(TagName=""),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("", "F41BF02E48B865A2E4866BA11CA996ED", "보로스에게 정비 요청"),RadioOnStart=,RadioOnComplete=))</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>("Radio_Endurance_Start")</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>(Credits=600,Items=((RowId="Cons_Repair_01",Count=3)))</t>
+          <t>("Radio_Endurance_Clear")</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "B77D100D42B0EF9B5B9CCCA1937BB68D", "크레딧 600 · 나노 수리킷 ×3")</t>
+          <t>(Sequence=None,RequiredWorld=None,StartDelay=0.000000,PlayRate=1.000000,bHideHUD=True,bHidePlayer=True,bDisableMovementInput=True,bDisableLookAtInput=True,bSkippable=True)</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>(Credits=400,PurchaseRefund=(Rate=1.000000,MaxCredits=0),Items=)</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>NSLOCTEXT("", "4B0737CB4184424CCEFEDDA08BB3EFA9", "구매액 100% 환급 · 완료 보너스 400 크레딧")</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -981,10 +1109,25 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Q_Mobility</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
+        <is>
+          <t>Quest_Reach</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>NPC_Mechanic</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -998,20 +1141,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "7F78C09B47F41C2E0A481F8FCC010474", "무장 확충")</t>
+          <t>NSLOCTEXT("", "489985C047345CEB707C0CA2C6DCD0ED", "무장 확충")</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("", "9D1F50CB4BA19C2CA2E1CDBD7287F663", "장비 강화")</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("", "4DBC02204A094E953BD934BC27BD0268", "상점 연계")</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1021,49 +1171,52 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>InProgress</t>
+          <t>NotStarted</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "9172EA1F4A846513FAF6C4A073784358", "공격형 모듈 2종을 확보해 무장을 확충한다.")</t>
+          <t>NSLOCTEXT("", "59798EE6450B12F94CBE8E86404D1CFE", "광폭 회로를 구해 세라에게 장착을 맡긴다.")</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "6C3B59154211DA1D90C80DB5AF7374A9", "고강도 교전 구역 투입을 앞두고 화력 규격이 상향됐다. 광폭 회로와 질풍 모듈을 모두 조달해 공격 편성을 완성하라.")</t>
+          <t>Quest.NPCButton.Q_Arsenal</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>((Type=AcquireItem,TargetId="Mod_Berserk_01",TargetTag=(TagName=""),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "1D42A09F4D19B81AB3BD4C90595F22E9", "광폭 회로 확보"),RadioOnStart=,RadioOnComplete=),(Type=AcquireItem,TargetId="Mod_Swift_01",TargetTag=(TagName=""),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "B3A538AA48CF58A0EF9CBA9AF0228CC1", "질풍 모듈 확보"),RadioOnStart=,RadioOnComplete=))</t>
+          <t>NSLOCTEXT("", "FFBDE4894516727D59EA86B75BD32DC3", "고강도 교전 구역 투입을 앞두고 화력 규격이 상향됐다. 보급상 데크에게서 광폭 회로를 확보한 뒤 모듈 관리관 세라에게 체결을 맡겨라.")</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+          <t>((Type=AcquireItem,TargetId="Mod_Berserk_01",TargetTag=(TagName=""),GuidanceNPCRowName="NPC_ItemShop",GuidanceScreenTag=(TagName="UI.Screen.Shop"),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("", "3B25B7054E34206D0E1400846DDDD0B1", "보급상 데크에게서 광폭 회로 구매"),RadioOnStart=,RadioOnComplete=),(Type=TalkToNPC,TargetId="NPC_ModuleManager",TargetTag=(TagName=""),GuidanceNPCRowName="",GuidanceScreenTag=(TagName=""),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("", "CD3DFD784871A054433FEBA236B48F0B", "세라에게 장착 요청"),RadioOnStart=,RadioOnComplete=))</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>(Credits=2500,Items=)</t>
+          <t>("Radio_Arsenal_Clear")</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "913E59E04B7D49202E6A7CB74D16137F", "크레딧 2,500")</t>
+          <t>(Sequence=None,RequiredWorld=None,StartDelay=0.000000,PlayRate=1.000000,bHideHUD=True,bHidePlayer=True,bDisableMovementInput=True,bDisableLookAtInput=True,bSkippable=True)</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>(Credits=600,PurchaseRefund=(Rate=1.000000,MaxCredits=0),Items=)</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>NSLOCTEXT("", "6833262F4DEF117BD73ADC9C9D419BF1", "구매액 100% 환급 · 완료 보너스 600 크레딧")</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1073,10 +1226,25 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Q_Mobility</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>NPC_ModuleManager</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1090,7 +1258,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "7B4677724190C964B887078FAD131822", "철벽 확보")</t>
+          <t>NSLOCTEXT("", "7B98071D4F33F9516906F1BBC74E55C7", "철벽 확보")</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1098,12 +1266,19 @@
           <t>Side</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("", "A6F63C1748905D855DE9FD882EC67FA0", "장비 강화")</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("", "3F59A8E148E83968B5F103800E6D0599", "상점 연계")</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1113,49 +1288,52 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>InProgress</t>
+          <t>NotStarted</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "83C30EF846A3D0F8CE1CFFB3361FACF1", "전설급 방어 시스템을 조달한다.")</t>
+          <t>NSLOCTEXT("", "F0D237F24FF755C04A54D2B7DB8602D8", "철벽 프로토콜을 구해 세라에게 장착을 맡긴다.")</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "28503E9347FC8D9541457EA832CABDD6", "방어 거점 사수 임무에 대비해 최고 등급 방어 규격이 요구된다. 철벽 프로토콜을 확보하라.")</t>
+          <t>Quest.NPCButton.Q_Fortress</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>((Type=AcquireItem,TargetId="Mod_Bastion_01",TargetTag=(TagName=""),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "F13D1F5642B426235E964AB6E6A21F85", "철벽 프로토콜 확보"),RadioOnStart=,RadioOnComplete=))</t>
+          <t>NSLOCTEXT("", "B174EF25443DA4F81C505F8A8F07C1E4", "방어 거점 사수 임무에 대비해 최고 등급 방어 규격이 요구된다. 보급상 데크에게서 철벽 프로토콜을 확보한 뒤 세라에게 체결을 맡겨라.")</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+          <t>((Type=AcquireItem,TargetId="Mod_Bastion_01",TargetTag=(TagName=""),GuidanceNPCRowName="NPC_ItemShop",GuidanceScreenTag=(TagName="UI.Screen.Shop"),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("", "A04036334AF62980AB3CBC81FB779D4A", "보급상 데크에게서 철벽 프로토콜 구매"),RadioOnStart=,RadioOnComplete=),(Type=TalkToNPC,TargetId="NPC_ModuleManager",TargetTag=(TagName=""),GuidanceNPCRowName="",GuidanceScreenTag=(TagName=""),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("", "9568178345E412766798758706E9DAF6", "세라에게 장착 요청"),RadioOnStart=,RadioOnComplete=))</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>(Credits=1500,Items=)</t>
+          <t>("Radio_Fortress_Clear")</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "27103C9A40256DD2ABBF589E62CDEC52", "크레딧 1,500")</t>
+          <t>(Sequence=None,RequiredWorld=None,StartDelay=0.000000,PlayRate=1.000000,bHideHUD=True,bHidePlayer=True,bDisableMovementInput=True,bDisableLookAtInput=True,bSkippable=True)</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>(Credits=800,PurchaseRefund=(Rate=1.000000,MaxCredits=0),Items=)</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>NSLOCTEXT("", "D6F2BB4A49BF10A5FA46A7A8F22D4A31", "구매액 100% 환급 · 완료 보너스 800 크레딧")</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1165,10 +1343,25 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Q_Arsenal</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>NPC_ModuleManager</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1182,20 +1375,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "FA1DE230405886983CC60DB733356CFA", "최종 병기 조달")</t>
+          <t>NSLOCTEXT("", "A806A0C54006C69BE64695BA041E9BCD", "최종 병기 조달")</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("", "D98D84924A0943CEDB502EBCA9DF2B01", "장비 강화")</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("", "EAEA541644E21153C4DBEE8E5B3C49EC", "상점 연계")</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1205,49 +1405,52 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>InProgress</t>
+          <t>NotStarted</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "1482F73145D4143F4E341797EA13969B", "관통자 레일건을 조달해 주무장을 교체한다.")</t>
+          <t>NSLOCTEXT("", "6245BC6149B9229ECD24788340CA450E", "관통자 레일건을 조달해 주무장을 교체한다.")</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "59C64F9241903B1631D3C780A2F77B3D", "차기 작전의 핵심 표적은 중장갑 유닛이다. 장갑을 무시하는 관통자 레일건을 조달해 주무장 규격을 최상위로 끌어올려라.")</t>
+          <t>Quest.NPCButton.Q_Apex</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>((Type=AcquireItem,TargetId="Wpn_Rail_01",TargetTag=(TagName=""),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "6D82E3604F48F865FB4A368757AC53CA", "관통자 레일건 확보"),RadioOnStart=,RadioOnComplete=))</t>
+          <t>NSLOCTEXT("", "48D151344A4FBBECFFA45EABADF81207", "차기 작전의 핵심 표적은 중장갑 유닛이다. 보급상 데크에게 장갑을 무시하는 관통자 레일건을 조달해 주무장 규격을 최상위로 끌어올려라.")</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>((Type=AcquireItem,TargetId="Wpn_Rail_01",TargetTag=(TagName=""),GuidanceNPCRowName="NPC_ItemShop",GuidanceScreenTag=(TagName="UI.Screen.Shop"),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("", "A2436CDC4DA2F36B04EE69BA9F6DDAAF", "관통자 레일건 확보"),RadioOnStart=,RadioOnComplete=))</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>(Credits=3000,Items=((RowId="Mod_Amp_01",Count=1)))</t>
+          <t>("Radio_Apex_Clear")</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "6929E2034F0800AA9A7D89ADAF98A88F", "크레딧 3,000 · 고출력 증폭기 ×1")</t>
+          <t>(Sequence=None,RequiredWorld=None,StartDelay=0.000000,PlayRate=1.000000,bHideHUD=True,bHidePlayer=True,bDisableMovementInput=True,bDisableLookAtInput=True,bSkippable=True)</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>(Credits=1000,PurchaseRefund=(Rate=1.000000,MaxCredits=0),Items=)</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>NSLOCTEXT("", "BAB61E7B46674D1CAD373DA8D0AF4CEB", "구매액 100% 환급 · 완료 보너스 1,000 크레딧")</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1257,10 +1460,25 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Q_Arsenal</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>NPC_ItemShop</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1282,9 +1500,16 @@
           <t>Main</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "Q_FirstSync_QuestGroupTitle", "복귀 기록")</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "Q_FirstSync_QuestGroupSubtitle", "Prologue: 각성")</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>1</t>
@@ -1302,42 +1527,39 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "88E574784FA2F107D5FEEE8BC63288EC", "외골격 동기화를 완료했다.")</t>
+          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "88E574784FA2F107D5FEEE8BC63288EC", "외골격 재동기화를 마쳤다. 이후 3주간의 기록은 비어 있다.")</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "4D55B7054F6413BC92F325B492C1817F", "전선 복귀 전 외골격 재동기화 절차. 이미 완료해 보상을 수령한 과거 임무 기록이다.")</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
+          <t>Quest.NPCButton.Q_FirstSync</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "4D55B7054F6413BC92F325B492C1817F", "전선 복귀 전 외골격 재동기화 절차. 당시 동기율은 권장치를 넘겼으나, 이후 3주간 실종 상태로 방치되며 수치가 떨어졌다. 보상까지 수령이 끝난 과거 임무 기록이다.")</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>(Credits=500,Items=)</t>
-        </is>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
+          <t>(Sequence=None,RequiredWorld=None,StartDelay=0.000000,PlayRate=1.000000,bHideHUD=True,bHidePlayer=True,bDisableMovementInput=True,bDisableLookAtInput=True,bSkippable=True)</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>(Credits=500,PurchaseRefund=(Rate=0.000000,MaxCredits=0),Items=)</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
           <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "E5767E2D4CF4BED2027F3592549F3359", "크레딧 500")</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="T8" t="inlineStr">
         <is>
           <t>None</t>
@@ -1349,6 +1571,21 @@
         </is>
       </c>
       <c r="V8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1362,20 +1599,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "332789474C3048B1D80EC185C1B10873", "오염원 제거")</t>
+          <t>NSLOCTEXT("", "6A65556C4A26143276EE5986ABEE458D", "사격조 제압")</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("", "F76884864004DEDC38ABB6AFCEC775D3", "전선 임무")</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("", "8483935D4B59FE415E4359940110B8B9", "Chapter 2: 교전")</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1390,40 +1634,52 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "C68A6CFD432C3F90D6E87491D8DB2498", "구역의 오염 발생원을 무력화한다. (전투 슬라이스 연동 예정)")</t>
+          <t>NSLOCTEXT("", "2E45C64341FB021A7A24CDB362598BE7", "원거리 사격형 적 2기를 제압한다.")</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "3F8652614DC9A9D4581A5AAEDBDB5EAC", "감염 구역의 핵심 오염 발생원을 추적해 제거하는 전투 임무. 인게임 전투 슬라이스가 붙으면 킬 목표로 활성화된다.")</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>Quest.NPCButton.Q_Contamination</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("", "B8003DDD488CFFFCBCC427A29415ED08", "엄폐물 뒤에서 아군 진입로를 봉쇄하는 사격형 유닛이 확인됐다. 균열에서 새어 나온 오염 농도가 짙은 구역이라 장기 노출은 금물이다. 기갑병 릭의 요청대로 사격조를 제압하라.")</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>((Type=KillTarget,TargetId="",TargetTag=(TagName="Enemy.Type.Shooter"),GuidanceNPCRowName="",GuidanceScreenTag=(TagName=""),AcceptRadius=3.000000,RequiredCount=2,Label=NSLOCTEXT("", "EBEC7A7D4EADAE81B1D060BF654671B4", "사격형 처치"),RadioOnStart=,RadioOnComplete=))</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>("Radio_Shooter_Start")</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>(Credits=4000,Items=((RowId="Mod_Berserk_01",Count=1)))</t>
+          <t>("Radio_Shooter_Clear")</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "AB91299B46B013C7EC41FDA03076DEE6", "크레딧 4,000 · 광폭 회로 ×1")</t>
+          <t>(Sequence=None,RequiredWorld=None,StartDelay=0.000000,PlayRate=1.000000,bHideHUD=True,bHidePlayer=True,bDisableMovementInput=True,bDisableLookAtInput=True,bSkippable=True)</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>(Credits=1600,PurchaseRefund=(Rate=0.000000,MaxCredits=0),Items=((RowId="Mod_Berserk_01",Count=1)))</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>NSLOCTEXT("", "E2CA36C0429D60DB649E8B82723985A8", "크레딧 1,600 · 광폭 회로 ×1")</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1433,10 +1689,25 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Q_Dungeon_Gate</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>NPC_Trooper_A</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1450,7 +1721,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "660429B5443654EC715DDA82B226C207", "보급창고로 이동")</t>
+          <t>NSLOCTEXT("", "CE6E28914D154416AE7A8AA21818413A", "정찰 훈련")</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1458,9 +1729,16 @@
           <t>Main</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("", "1B3F2A194CCF592EF1CCA8B9FF5F6610", "기지 적응")</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("", "A2F38F99413C1CC502AA2D9F71144A48", "Chapter 1: 재정비")</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>1</t>
@@ -1473,80 +1751,89 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>InProgress</t>
+          <t>NotStarted</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "0E27DA73459CA96379DDA4ACE6E083DF", "표시된 보급창고 지점으로 이동하라.")</t>
+          <t>NSLOCTEXT("", "0CFDE52C480E9F9C8724FCB1CB051A94", "보급창고까지 이동한 뒤 보초병에게 보고한다.")</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "D05CA06D4CC2ADFA42E6FD96022A3BA7", "화면 마커가 가리키는 지점까지 이동하면 완료된다. 거리(m)가 실시간 표시된다. 완료 시 자동 보상 후 다음 임무로 이어진다.")</t>
+          <t>Quest.NPCButton.Quest_Reach</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>((Type=ReachLocation,TargetId="",TargetTag=(TagName="Location.Quest.Depot"),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "6C0ABEFB4D465B20A4766D9F40D6D991", "보급창고 도달"),RadioOnStart=,RadioOnComplete=))</t>
+          <t>NSLOCTEXT("", "54FD07264980B41C056C11ABEE494F32", "화면 마커가 가리키는 보급창고 지점까지 이동하고, 도착하면 보초병 콜에게 정찰 결과를 보고하라. 거리(m)가 실시간으로 표시된다.")</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>((Type=ReachLocation,TargetId="",TargetTag=(TagName="Location.Quest.Depot"),GuidanceNPCRowName="",GuidanceScreenTag=(TagName=""),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("", "36C2404F48705B4C4988A9982ED274A1", "보급창고 도달"),RadioOnStart=,RadioOnComplete=("Radio_Depot_Arrive")),(Type=TalkToNPC,TargetId="NPC_Sentry_A",TargetTag=(TagName=""),GuidanceNPCRowName="",GuidanceScreenTag=(TagName=""),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("", "B9F2F4574FF8170EA8F57F8C867747FF", "보초병 콜에게 보고"),RadioOnStart=,RadioOnComplete=("Radio_Reach_Clear")))</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>(Sequence=None,RequiredWorld=None,StartDelay=0.000000,PlayRate=1.000000,bHideHUD=True,bHidePlayer=True,bDisableMovementInput=True,bDisableLookAtInput=True,bSkippable=True)</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>(Credits=400,PurchaseRefund=(Rate=0.000000,MaxCredits=0),Items=)</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("", "970654024323246969CD9C8A4AC896CD", "크레딧 400")</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Q_Endurance</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>NPC_Instructor</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
           <t>False</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>("Radio_Base_Welcome")</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>(Credits=100,Items=)</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "E89608DA4213AD314BEE5AB73DDD7054", "크레딧 100")</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Quest_Hunt</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>True</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Quest_Hunt</t>
+          <t>Quest_Talk</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "78B651D04921A3E4AC887D97A316894E", "그런트 소탕")</t>
+          <t>NSLOCTEXT("", "3D50983F4DED274DA9930499E8495B90", "장교에게 보고")</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1554,12 +1841,19 @@
           <t>Main</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("", "4DD694204B2B906841BFFFBE779A6D43", "전선 임무")</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("", "C9594D5648B4472B64DDADB6A8E7A340", "Chapter 2: 교전")</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1574,149 +1868,197 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "2ED26D864FF504854E34378135A51F97", "그런트 3기를 처치하라.")</t>
+          <t>NSLOCTEXT("", "04E457DF4FDBB88D5B2FA198D1B848A8", "기갑 장교 발렌에게 교전 결과를 보고한다.")</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "CD9088EE4CA8BFFB0459389E5917FB35", "선행 임무(보급창고 이동) 완료 후 자동으로 시작된다. 그런트 3기 처치 시 완료.")</t>
+          <t>Quest.NPCButton.Quest_Talk</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>((Type=KillTarget,TargetId="",TargetTag=(TagName="Enemy.Type.Grunt"),AcceptRadius=3.000000,RequiredCount=3,Label=NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "B94BDE7C4FC904B37A0A1790F7647D08", "그런트 처치"),RadioOnStart=,RadioOnComplete=))</t>
+          <t>NSLOCTEXT("", "F3D1A7464C68385B44E4509001CA5BF4", "돌격조 소탕이 끝나면 기갑 장교 발렌에게 교전 결과를 보고하라. 보고와 동시에 임무가 마무리된다.")</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>((Type=TalkToNPC,TargetId="NPC_Officer",TargetTag=(TagName=""),GuidanceNPCRowName="",GuidanceScreenTag=(TagName=""),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("", "E2C588954FD952339DB740A329088E16", "발렌에게 보고"),RadioOnStart=,RadioOnComplete=))</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>(Credits=200,Items=)</t>
+          <t>("Radio_Talk_Clear")</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "80611DD14DD189147D77528FD17344D5", "크레딧 200")</t>
+          <t>(Sequence=None,RequiredWorld=None,StartDelay=0.000000,PlayRate=1.000000,bHideHUD=True,bHidePlayer=True,bDisableMovementInput=True,bDisableLookAtInput=True,bSkippable=True)</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>(Credits=700,PurchaseRefund=(Rate=0.000000,MaxCredits=0),Items=)</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Quest_Reach</t>
+          <t>NSLOCTEXT("", "195488D044F57C3090A1F58B361E77AB", "크레딧 700")</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Quest_Talk</t>
+          <t>None</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Q_Dungeon_Gate</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>NPC_Officer</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
           <t>True</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Q_Dungeon_Gate</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "DFB833EE46EBF22CB2AE5FA50A3072FB", "궤도 엘리베이터 돌파")</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("", "18EEBE41440C6A52244A2EA791F149E0", "균열 돌파")</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("", "226201F046C6F4BD1C553BBEE2B2BAC2", "Chapter 3: 궤도 엘리베이터")</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>NotStarted</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "B845BE8546DDC9925D4DBE8FC2CBB13D", "각 구역으로 이동해 출현한 적을 소탕하고 균열 핵심부를 봉쇄하라.")</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Quest.NPCButton.Q_Dungeon_Gate</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "E3B078D843AA70AF98DF629A2D9FBF66", "현재 EncounterTable에 정의된 Zone 3에서 시작해 Zone 2를 거쳐 보스 구역까지 순서대로 진입한다. 각 구역의 처치 목표 수는 실제 웨이브 구성에서 자동 계산된다.")</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>((Type=ReachLocation,TargetId="Room.Zone3",TargetTag=(TagName="Location.Quest.Dungeon.Zone3"),GuidanceNPCRowName="",GuidanceScreenTag=(TagName=""),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("", "8BD8375341CDE79CEB7156A91757AFEA", "Zone 3 진입"),RadioOnStart=,RadioOnComplete=("Radio_Gate_Arrival","Radio_Gate_Encounter")),(Type=ClearEncounter,TargetId="Room.Zone3",TargetTag=(TagName=""),GuidanceNPCRowName="",GuidanceScreenTag=(TagName=""),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("", "CCED16A54E265DE45A0AB6B1CB9EF898", "Zone 3 적 소탕"),RadioOnStart=,RadioOnComplete=("Radio_Gate_Clear")),(Type=ReachLocation,TargetId="Room.Zone2",TargetTag=(TagName="Location.Quest.Dungeon.Zone2"),GuidanceNPCRowName="",GuidanceScreenTag=(TagName=""),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("", "18D5FA8A412CDB155F919EB9A3988028", "Zone 2 진입"),RadioOnStart=,RadioOnComplete=("Radio_MidBrief")),(Type=ClearEncounter,TargetId="Room.Zone2",TargetTag=(TagName=""),GuidanceNPCRowName="",GuidanceScreenTag=(TagName=""),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("", "8DC0C5E740F5481E820EC79E2A740438", "반응로 코어 사수"),RadioOnStart=,RadioOnComplete=("Radio_Reactor_Hold")),(Type=ReachLocation,TargetId="Room.Boss",TargetTag=(TagName="Location.Quest.Dungeon.Boss"),GuidanceNPCRowName="",GuidanceScreenTag=(TagName=""),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("", "C12B1079486BF34DB049579A8AAB70F1", "보스 구역 진입"),RadioOnStart=,RadioOnComplete=("Radio_Boss_Approach","Radio_Boss_Warning")),(Type=ClearEncounter,TargetId="Room.Boss",TargetTag=(TagName=""),GuidanceNPCRowName="",GuidanceScreenTag=(TagName=""),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("", "8679A5D94C47AF6EBAB3509785CBF5CD", "궤도 엘리베이터 점령 (보스 처치)"),RadioOnStart=,RadioOnComplete=))</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>("Radio_System_Alert")</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>("Radio_Boss_Clear","Radio_Dungeon_Complete")</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>(Sequence=None,RequiredWorld=None,StartDelay=0.000000,PlayRate=1.000000,bHideHUD=True,bHidePlayer=True,bDisableMovementInput=True,bDisableLookAtInput=True,bSkippable=True)</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>(Credits=5000,PurchaseRefund=(Rate=0.000000,MaxCredits=0),Items=)</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "0C01601B4CF92572A231E196B998BE07", "크레딧 5,000")</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Q_Elevator_Deploy</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
           <t>Quest_Talk</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "741F1F944F4DBB5A483218A9AFCF8413", "장교에게 보고")</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Side</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>NotStarted</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "E3622F204DA5A7251A325A983608EEE0", "장교 NPC에게 말을 걸어 작전 결과를 보고하라.")</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "58928D5F4A01E5CF54B68E8B121F32E2", "선행 임무 완료 후 장교(NPC_Officer)에게 말을 걸면 수락과 동시에 완료되고 보상이 지급된다.")</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>((Type=TalkToNPC,TargetId="NPC_Officer",TargetTag=(TagName=""),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "D70AF0A04B605974131F97BC15890603", "장교에게 보고"),RadioOnStart=,RadioOnComplete=))</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>(Credits=300,Items=)</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "D9E859D84D2EE119B7B4A1BA789AB86D", "크레딧 300")</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>Quest_Hunt</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>NPC_Officer</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -1725,293 +2067,117 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Q_Elevator_Deploy</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_QuestData", "Q_Elevator_Deploy_Title", "작전 하달: 궤도 엘리베이터")</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_QuestData", "Q_Elevator_Deploy_Group", "진격")</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_QuestData", "Q_Elevator_Deploy_Sub", "Chapter 2")</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>NotStarted</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_QuestData", "Q_Elevator_Deploy_Summary", "장교 발렌과 대화하여 궤도 엘리베이터 진입 작전을 수행하십시오.")</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Quest.NPCButton.Q_Elevator_Deploy</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_QuestData", "Q_Elevator_Deploy_Desc", "장교에게서 작전을 하달받고 전송 게이트로 이동해야 합니다.")</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>((Type=TalkToNPC,TargetId="NPC_Sentry_A",TargetTag=(TagName=""),GuidanceNPCRowName="NPC_Sentry_A",GuidanceScreenTag=(TagName=""),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("", "", "전송 게이트 앞 초병(Sentry)에게 보고"),RadioOnStart=,RadioOnComplete=))</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>("Radio_Hunt_Start")</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>("Radio_Elevator_Move")</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>(Sequence="/Game/Cinematics/Quest/Quest_Hunt/LS_Quest_Hunt_Start.LS_Quest_Hunt_Start",RequiredWorld="/Game/Maps/IngameMap/HubMap1.HubMap1",StartDelay=0.350000,PlayRate=1.000000,bHideHUD=True,bHidePlayer=True,bDisableMovementInput=True,bDisableLookAtInput=True,bSkippable=True)</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>(Credits=0,PurchaseRefund=(Rate=0.000000,MaxCredits=0),Items=)</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_QuestData", "Q_Elevator_Deploy_Reward", "")</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Quest_Reach</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
           <t>Q_Dungeon_Gate</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "DFB833EE46EBF22CB2AE5FA50A3072FB", "궤도 엘리베이터 돌파")</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>InProgress</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "B845BE8546DDC9925D4DBE8FC2CBB13D", "각 구역으로 이동해 출현한 적을 소탕하고 균열 핵심부를 봉쇄하라.")</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "E3B078D843AA70AF98DF629A2D9FBF66", "현재 EncounterTable에 정의된 Zone 3에서 시작해 Zone 2를 거쳐 보스 구역까지 순서대로 진입한다. 각 구역의 처치 목표 수는 실제 웨이브 구성에서 자동 계산된다.")</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>((Type=ReachLocation,TargetId="Room.Zone3",TargetTag=(TagName="Location.Quest.Dungeon.Zone3"),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("", "3F7E6DBF427C6BCE9F20B48645E4BF8A", "Zone 3 진입"),RadioOnStart=,RadioOnComplete=("Radio_Gate_Arrival","Radio_Gate_Encounter")),(Type=ClearEncounter,TargetId="Room.Zone3",TargetTag=(TagName=""),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("", "7875DF664F51B5248587BAA9B86FCDE7", "Zone 3 적 소탕"),RadioOnStart=,RadioOnComplete=("Radio_Gate_Clear")),(Type=ReachLocation,TargetId="Room.Zone2",TargetTag=(TagName="Location.Quest.Dungeon.Zone2"),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("", "9FA97B7D453A8C918EA7978E6D17582B", "Zone 2 진입"),RadioOnStart=,RadioOnComplete=("Radio_MidBrief")),(Type=DefendZone,TargetId="",TargetTag=(TagName="Location.Quest.Reactor"),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("", "472B4D69438E8064CFF203B8EC19C4BD", "반응로 코어 사수"),RadioOnStart=,RadioOnComplete=),(Type=ReachLocation,TargetId="Room.Boss",TargetTag=(TagName="Location.Quest.Dungeon.Boss"),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("", "8608F665421815F567D97082DA535EBC", "보스 구역 진입"),RadioOnStart=,RadioOnComplete=("Radio_Boss_Approach")),(Type=ClearEncounter,TargetId="Room.Boss",TargetTag=(TagName=""),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("", "5F2D61EA487F1CE761ED24B1CE391BC7", "보스 처치"),RadioOnStart=,RadioOnComplete=))</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>NPC_Officer</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>("Radio_System_Alert")</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>("Radio_Boss_Clear","Radio_Dungeon_Complete")</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>(Credits=5000,Items=)</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "0C01601B4CF92572A231E196B998BE07", "크레딧 5,000")</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Quest_Defend</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "E1D38FDE4E1F7967E2B4E7AD9F5CE273", "리액터 방어")</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>NotStarted</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "3978BC70470E0500658BCBB7D8C2EBC1", "리액터를 지켜 방어하라.")</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "7E5BC101493FB4C43FDF6F80402018D4", "정해진 시간 동안 적의 공격으로부터 리액터가 파괴되지 않도록 사수하라. 대상이 파괴되면 실패한다.")</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>((Type=DefendZone,TargetId="",TargetTag=(TagName="Location.Quest.Reactor"),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "4CC5856D43F7D1A92359F4B3E54DA518", "리액터 방어"),RadioOnStart=,RadioOnComplete=))</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>(Credits=300,Items=)</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "43405EA240FD9E752E08B3B20A98093D", "크레딧 300")</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Quest_Capture</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "EE4CABB04FE83605E1CEAAA4B3E944A4", "전초기지 점령")</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>LOCTABLE("/Game/Data/Tables/Localize/ST_Localize.ST_Localize", "Quest.Main")</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>NotStarted</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "336C24F74AAA24F4386038B1813AFDAD", "전초기지를 점령하라.")</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "1A46DC944A25C24A400DC98F6985EF3F", "점령 구역에 진입해 정해진 시간 동안 머무르면 점령이 완료된다. 구역을 벗어나면 진행이 멈춘다.")</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>((Type=CaptureZone,TargetId="",TargetTag=(TagName="Location.Quest.Outpost"),AcceptRadius=3.000000,RequiredCount=1,Label=NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "2A9CA9ED48C105D9E14D5C9246502957", "전초기지 점령"),RadioOnStart=,RadioOnComplete=))</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>(Credits=300,Items=)</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>NSLOCTEXT("DT_QuestData [BEF0E53BB3B8EDC9C2DFD2179222692A]", "A000E21F47CF2E3D427A389FFAEB0863", "크레딧 300")</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V15"/>
+  <autoFilter ref="A1:X16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2022,8 +2188,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
@@ -2049,17 +2215,22 @@
           <t>NPCRole</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>InteractionLabel</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>InteractionRadius</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Actions</t>
         </is>
@@ -2073,27 +2244,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>정비병 보로스</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Mechanic_DisplayName", "정비병 보로스")</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>정비병</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Mechanic_NPCRole", "정비병")</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>대화</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Mechanic_Description", "외골격 정비반을 20년째 지키고 있는 노련한 정비병이다. 모듈 회로보다 뼈대와 관절을 먼저 보는 고집이 있는데, 그 고집 덕에 살아 돌아온 작전원이 적지 않다.")</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Mechanic_InteractionLabel", "대화")</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>((Label="대화하기",Type="Dialogue",ScreenTag="",DialogueRowName="DLG_Mechanic"))</t>
+          <t>150.000000</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>((Label=NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Mechanic_Actions_Index0_Label", "대화하기"),Type=Dialogue,ScreenTag=(TagName=""),DialogueRowName="DLG_Mechanic"))</t>
         </is>
       </c>
     </row>
@@ -2105,27 +2281,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>청소병 핀</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Janitor_DisplayName", "청소병 핀")</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>청소병</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Janitor_NPCRole", "청소병")</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>대화</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Janitor_Description", "기지 제염 구역을 담당하는 청소병이다. 아무도 눈여겨보지 않는 일이라는 걸 알면서도, 자기가 닦은 바닥 위에서 다들 숨 쉬고 산다는 사실을 조용히 자부한다.")</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Janitor_InteractionLabel", "대화")</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>((Label="대화하기",Type="Dialogue",ScreenTag="",DialogueRowName="DLG_Janitor"))</t>
+          <t>150.000000</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>((Label=NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Janitor_Actions_Index0_Label", "대화하기"),Type=Dialogue,ScreenTag=(TagName=""),DialogueRowName="DLG_Janitor"))</t>
         </is>
       </c>
     </row>
@@ -2137,27 +2318,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>모듈 관리관 세라</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_ModuleManager_DisplayName", "모듈 관리관 세라")</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>모듈 관리</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_ModuleManager_NPCRole", "모듈 관리")</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대화</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_ModuleManager_Description", "기지의 모듈 등록과 체결을 총괄하는 관리관이다. 평소엔 수치와 규격으로만 말하지만, 작전 중 무전을 잡으면 누구보다 먼저 이상 징후를 읽어 낸다.")</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_ModuleManager_InteractionLabel", "대화")</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>((Label="대화하기",Type="Dialogue",ScreenTag="",DialogueRowName="DLG_ModuleManager"),(Label="모듈",Type="Screen",ScreenTag="UI.Screen.Module",DialogueRowName="None"))</t>
+          <t>150.000000</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>((Label=NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_ModuleManager_Actions_Index0_Label", "대화하기"),Type=Dialogue,ScreenTag=(TagName=""),DialogueRowName="DLG_ModuleManager"),(Label=NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_ModuleManager_Actions_Index1_Label", "모듈"),Type=Screen,ScreenTag=(TagName="UI.Screen.Module"),DialogueRowName=""))</t>
         </is>
       </c>
     </row>
@@ -2169,27 +2355,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>보급상 데크</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_ItemShop_DisplayName", "보급상 데크")</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>아이템 상점</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_ItemShop_NPCRole", "아이템 상점")</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대화</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_ItemShop_Description", "크레딧만 내면 뭐든 구해 온다는 기지의 보급상이다. 값은 정직하게 받는다는 원칙을 험한 세상에서도 지키고 있으며, 돌아온 작전원의 몫은 반드시 따로 챙겨 둔다.")</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_ItemShop_InteractionLabel", "대화")</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>((Label="대화하기",Type="Dialogue",ScreenTag="",DialogueRowName="DLG_ItemShop"),(Label="상점",Type="Screen",ScreenTag="UI.Screen.Shop",DialogueRowName="None"))</t>
+          <t>150.000000</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>((Label=NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_ItemShop_Actions_Index0_Label", "대화하기"),Type=Dialogue,ScreenTag=(TagName=""),DialogueRowName="DLG_ItemShop"),(Label=NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_ItemShop_Actions_Index1_Label", "상점"),Type=Screen,ScreenTag=(TagName="UI.Screen.Shop"),DialogueRowName=""))</t>
         </is>
       </c>
     </row>
@@ -2201,27 +2392,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>보초병 콜</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Sentry_A_DisplayName", "보초병 콜")</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>보초병</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Sentry_A_NPCRole", "보초병")</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대화</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Sentry_A_Description", "보급창고 초소를 지키는 보초병이다. 방어선이 3주 사이 초소 뒤까지 밀렸다는 걸 알면서도, 자기 자리를 뜨는 법이 없다.")</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Sentry_A_InteractionLabel", "대화")</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>((Label="대화하기",Type="Dialogue",ScreenTag="",DialogueRowName="DLG_Sentry_A"))</t>
+          <t>150.000000</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>((Label=NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Sentry_A_Actions_Index0_Label", "대화하기"),Type=Dialogue,ScreenTag=(TagName=""),DialogueRowName="DLG_Sentry_A"))</t>
         </is>
       </c>
     </row>
@@ -2233,27 +2429,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>보초병 렌</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Sentry_B_DisplayName", "보초병 렌")</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>보초병</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Sentry_B_NPCRole", "보초병")</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대화</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Sentry_B_Description", "외곽 경계를 맡은 신참 보초병이다. 근무 중 잡담은 금지라고 스스로 되뇌면서도 사람만 보면 말을 붙이는데, 정작 이상 징후는 한 번도 놓친 적이 없다.")</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Sentry_B_InteractionLabel", "대화")</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>((Label="대화하기",Type="Dialogue",ScreenTag="",DialogueRowName="DLG_Sentry_B"))</t>
+          <t>150.000000</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>((Label=NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Sentry_B_Actions_Index0_Label", "대화하기"),Type=Dialogue,ScreenTag=(TagName=""),DialogueRowName="DLG_Sentry_B"))</t>
         </is>
       </c>
     </row>
@@ -2265,27 +2466,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>교육 조교 탈</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Instructor_DisplayName", "교육 조교 탈")</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>교육 조교</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Instructor_NPCRole", "교육 조교")</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대화</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Instructor_Description", "신병 교육대를 오래 지켜 온 교육 조교다. 생환이 최고의 성적이라는 말을 입에 달고 살며, 자기 손을 거친 이름이 실종자 명단에 오를 때마다 그 이름을 따로 적어 둔다.")</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Instructor_InteractionLabel", "대화")</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>((Label="대화하기",Type="Dialogue",ScreenTag="",DialogueRowName="DLG_Instructor"))</t>
+          <t>150.000000</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>((Label=NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Instructor_Actions_Index0_Label", "대화하기"),Type=Dialogue,ScreenTag=(TagName=""),DialogueRowName="DLG_Instructor"))</t>
         </is>
       </c>
     </row>
@@ -2297,27 +2503,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>기갑병 릭</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Trooper_A_DisplayName", "기갑병 릭")</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>기갑병</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Trooper_A_NPCRole", "기갑병")</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>대화</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Trooper_A_Description", "계승자의 후방 엄호를 자처하는 기갑병이다. 외골격 출력 점검을 하루에도 몇 번씩 반복하는 성격이라, 그가 이상 없다고 하면 정말로 이상이 없다.")</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Trooper_A_InteractionLabel", "대화")</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>((Label="대화하기",Type="Dialogue",ScreenTag="",DialogueRowName="DLG_Trooper_A"))</t>
+          <t>150.000000</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>((Label=NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Trooper_A_Actions_Index0_Label", "대화하기"),Type=Dialogue,ScreenTag=(TagName=""),DialogueRowName="DLG_Trooper_A"))</t>
         </is>
       </c>
     </row>
@@ -2329,27 +2540,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>기갑병 보드</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Trooper_B_DisplayName", "기갑병 보드")</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>기갑병</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Trooper_B_NPCRole", "기갑병")</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>대화</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Trooper_B_Description", "이 구역 방어선이 뚫린 적 없다고 단언하는 고참 기갑병이다. 말투는 무뚝뚝하지만 교대 인원이 부족할 때마다 자기가 한 타임씩 더 서는 쪽을 택한다.")</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Trooper_B_InteractionLabel", "대화")</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>((Label="대화하기",Type="Dialogue",ScreenTag="",DialogueRowName="DLG_Trooper_B"))</t>
+          <t>150.000000</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>((Label=NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Trooper_B_Actions_Index0_Label", "대화하기"),Type=Dialogue,ScreenTag=(TagName=""),DialogueRowName="DLG_Trooper_B"))</t>
         </is>
       </c>
     </row>
@@ -2361,27 +2577,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>기갑 장교 발렌</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Officer_DisplayName", "기갑 장교 발렌")</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>기갑 장교</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Officer_NPCRole", "기갑 장교")</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대화</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Officer_Description", "기갑 소대를 지휘하는 장교다. 규율이 곧 생존이라 믿으며, 부대원이 감당하지 못할 기록은 자기 선에서 정리해 보고서에 남기지 않는다.")</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Officer_InteractionLabel", "대화")</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>((Label="대화하기",Type="Dialogue",ScreenTag="",DialogueRowName="DLG_Officer"))</t>
+          <t>150.000000</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>((Label=NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Officer_Actions_Index0_Label", "대화하기"),Type=Dialogue,ScreenTag=(TagName=""),DialogueRowName="DLG_Officer"))</t>
         </is>
       </c>
     </row>
@@ -2393,27 +2614,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>피난민 미아</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Civilian_A_DisplayName", "피난민 미아")</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>시민</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Civilian_A_NPCRole", "시민")</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>대화</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Civilian_A_Description", "오염 지대를 걸어서 넘어온 피난민이다. 오는 길에 잃은 것을 좀처럼 입에 올리지 않으며, 기지 안은 안전하다는 말을 스스로에게 되뇌듯 반복한다.")</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Civilian_A_InteractionLabel", "대화")</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>((Label="대화하기",Type="Dialogue",ScreenTag="",DialogueRowName="DLG_Civilian_A"))</t>
+          <t>150.000000</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>((Label=NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Civilian_A_Actions_Index0_Label", "대화하기"),Type=Dialogue,ScreenTag=(TagName=""),DialogueRowName="DLG_Civilian_A"))</t>
         </is>
       </c>
     </row>
@@ -2425,27 +2651,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>정착민 도른</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Civilian_B_DisplayName", "정착민 도른")</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>시민</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Civilian_B_NPCRole", "시민")</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>대화</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Civilian_B_Description", "기지 외곽 거주 구역에 자리를 잡은 정착민이다. 바깥으로 나갈 엄두는 내지 못하지만, 나가는 사람들을 향한 고마움만은 매번 빠뜨리지 않고 전한다.")</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Civilian_B_InteractionLabel", "대화")</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>((Label="대화하기",Type="Dialogue",ScreenTag="",DialogueRowName="DLG_Civilian_B"))</t>
+          <t>150.000000</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>((Label=NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Civilian_B_Actions_Index0_Label", "대화하기"),Type=Dialogue,ScreenTag=(TagName=""),DialogueRowName="DLG_Civilian_B"))</t>
         </is>
       </c>
     </row>
@@ -2457,27 +2688,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>노인 하란</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Civilian_C_DisplayName", "노인 하란")</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>시민</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Civilian_C_NPCRole", "시민")</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>대화</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Civilian_C_Description", "오염 이전의 땅을 기억하는 몇 안 되는 노인이다. 푸르렀던 시절 이야기를 꺼낼 때마다 젊은이들이 그 땅을 되찾아 줄 거라는 말로 끝을 맺는다.")</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Civilian_C_InteractionLabel", "대화")</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>((Label="대화하기",Type="Dialogue",ScreenTag="",DialogueRowName="DLG_Civilian_C"))</t>
+          <t>150.000000</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>((Label=NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Civilian_C_Actions_Index0_Label", "대화하기"),Type=Dialogue,ScreenTag=(TagName=""),DialogueRowName="DLG_Civilian_C"))</t>
         </is>
       </c>
     </row>
@@ -2489,27 +2725,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>행상인 코바</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Merchant_A_DisplayName", "행상인 코바")</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>상인</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Merchant_A_NPCRole", "상인")</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>대화</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Merchant_A_Description", "위험 구역을 넘나들며 물건을 구해 오는 떠돌이 장사꾼이다. 값을 세게 부르는 편이지만, 그가 가져온 물건이 값을 못 한 적은 없다.")</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Merchant_A_InteractionLabel", "대화")</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>((Label="대화하기",Type="Dialogue",ScreenTag="",DialogueRowName="DLG_Merchant_A"))</t>
+          <t>150.000000</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>((Label=NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Merchant_A_Actions_Index0_Label", "대화하기"),Type=Dialogue,ScreenTag=(TagName=""),DialogueRowName="DLG_Merchant_A"))</t>
         </is>
       </c>
     </row>
@@ -2521,27 +2762,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>밀매상 지크</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Merchant_B_DisplayName", "밀매상 지크")</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>상인</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Merchant_B_NPCRole", "상인")</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>대화</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Merchant_B_Description", "정식 보급으로는 나오지 않는 물건을 취급하는 밀매상이다. 출처를 묻지 말라는 것이 유일한 거래 조건이며, 물건의 상태만큼은 한 번도 속인 적이 없다.")</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Merchant_B_InteractionLabel", "대화")</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>((Label="대화하기",Type="Dialogue",ScreenTag="",DialogueRowName="DLG_Merchant_B"))</t>
+          <t>150.000000</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>((Label=NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_Merchant_B_Actions_Index0_Label", "대화하기"),Type=Dialogue,ScreenTag=(TagName=""),DialogueRowName="DLG_Merchant_B"))</t>
         </is>
       </c>
     </row>
@@ -2553,27 +2799,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>단골 타냐</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_ShopCustomer_A_DisplayName", "단골 타냐")</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>상점 손님</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_ShopCustomer_A_NPCRole", "상점 손님")</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>대화</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_ShopCustomer_A_Description", "보급 창구를 제집처럼 드나드는 단골이다. 어느 상점 물건이 실한지 꿰고 있으며, 묻지 않아도 자기 평가를 먼저 알려 준다.")</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_ShopCustomer_A_InteractionLabel", "대화")</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>((Label="대화하기",Type="Dialogue",ScreenTag="",DialogueRowName="DLG_ShopCustomer_A"))</t>
+          <t>150.000000</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>((Label=NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_ShopCustomer_A_Actions_Index0_Label", "대화하기"),Type=Dialogue,ScreenTag=(TagName=""),DialogueRowName="DLG_ShopCustomer_A"))</t>
         </is>
       </c>
     </row>
@@ -2585,27 +2836,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>손님 웨스</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_ShopCustomer_B_DisplayName", "손님 웨스")</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>상점 손님</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_ShopCustomer_B_NPCRole", "상점 손님")</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>대화</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_ShopCustomer_B_Description", "사고 싶은 것은 많고 크레딧은 늘 부족한 상점 손님이다. 다음 출격 보상이 들어오면 지르겠다는 말을 몇 달째 반복하고 있다.")</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_ShopCustomer_B_InteractionLabel", "대화")</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>((Label="대화하기",Type="Dialogue",ScreenTag="",DialogueRowName="DLG_ShopCustomer_B"))</t>
+          <t>150.000000</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>((Label=NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_ShopCustomer_B_Actions_Index0_Label", "대화하기"),Type=Dialogue,ScreenTag=(TagName=""),DialogueRowName="DLG_ShopCustomer_B"))</t>
         </is>
       </c>
     </row>
@@ -2617,27 +2873,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>기술광 뎁</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_ModuleCustomer_A_DisplayName", "기술광 뎁")</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>모듈 상점 손님</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_ModuleCustomer_A_NPCRole", "모듈 상점 손님")</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>대화</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_ModuleCustomer_A_Description", "신형 모듈 소식이라면 무엇이든 꿰고 있는 기술광이다. 회로 설계를 예술이라 부르며, 정작 자기 동기율이 받쳐 주지 않는다는 사실은 애써 넘긴다.")</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_ModuleCustomer_A_InteractionLabel", "대화")</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>((Label="대화하기",Type="Dialogue",ScreenTag="",DialogueRowName="DLG_ModuleCustomer_A"))</t>
+          <t>150.000000</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>((Label=NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_ModuleCustomer_A_Actions_Index0_Label", "대화하기"),Type=Dialogue,ScreenTag=(TagName=""),DialogueRowName="DLG_ModuleCustomer_A"))</t>
         </is>
       </c>
     </row>
@@ -2649,27 +2910,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>개조가 니케</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_ModuleCustomer_B_DisplayName", "개조가 니케")</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>모듈 상점 손님</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_ModuleCustomer_B_NPCRole", "모듈 상점 손님")</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>대화</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_ModuleCustomer_B_Description", "자기 외골격을 직접 튜닝하는 개조가다. 규격은 참고용일 뿐이라는 지론을 가지고 있으며, 처음 만난 상대에게도 장착 취향부터 묻는다.")</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_ModuleCustomer_B_InteractionLabel", "대화")</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>((Label="대화하기",Type="Dialogue",ScreenTag="",DialogueRowName="DLG_ModuleCustomer_B"))</t>
+          <t>150.000000</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>((Label=NSLOCTEXT("DT_NPCData [23523E33C7430B03FAEE8EDD5D9DCCD7]", "NPC_ModuleCustomer_B_Actions_Index0_Label", "대화하기"),Type=Dialogue,ScreenTag=(TagName=""),DialogueRowName="DLG_ModuleCustomer_B"))</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2952,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
@@ -2757,7 +3023,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>("모듈 등록 상태를 확인하러 왔군. 목록은 항상 최신으로 유지해 둔다.","슬롯 용량과 동기화율은 별개야. 좋은 모듈도 몸이 못 받으면 무용지물이지.","장착 구성은 단말에서 직접 만져. 실전 데이터가 쌓일수록 더 나은 조합이 열린다.")</t>
+          <t>("모듈 등록 상태를 보러 오셨죠. 목록은 항상 최신으로 유지해 둡니다.","슬롯 용량하고 동기율은 별개예요. 좋은 모듈도 몸이 못 받으면 그냥 짐입니다.","장착 구성은 단말에서 직접 만지세요. 실전 데이터가 쌓일수록 더 나은 조합이 열려요.")</t>
         </is>
       </c>
     </row>
@@ -2791,7 +3057,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>("정지 — 아, 계승자님이시군요. 통과하십시오.","이 게이트 너머는 제 담당입니다. 여긴 제가 지키니 안심하고 나가세요.")</t>
+          <t>("정지 — 아, 계승자님이시군요. 통과하십시오.","보급창고 초소는 제 담당입니다. 정찰 나가시면 결과는 저한테 넘겨 주십시오.")</t>
         </is>
       </c>
     </row>
@@ -2808,7 +3074,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>("교대까진 아직 멀었네요… 아, 근무 중 잡담은 금지였죠.","이상 징후 없습니다. 계승자님 계신 동안은 다들 발 뻗고 잡니다.")</t>
+          <t>("교대까진 아직 멀었네요… 아, 근무 중 잡담은 금지였죠.","이상 징후 없습니다. 계승자님 계신 동안은 다들 발 뻗고 잡니다.","전초기지 점령 건은 아직 유효합니다. 나가시면 제가 계기 중계하겠습니다.")</t>
         </is>
       </c>
     </row>
@@ -2842,7 +3108,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>("외골격 출력 점검 끝. 언제든 전개 가능합니다.","계승자님 뒤는 우리가 맡죠. 앞만 보고 나가십쇼.")</t>
+          <t>("외골격 출력 점검 끝. 언제든 전개 가능합니다.","계승자님 뒤는 우리가 맡죠. 앞만 보고 나가십쇼.","사격형 놈들이 아직 진입로를 막고 있습니다. 손 좀 빌려 주시면 좋겠는데요.")</t>
         </is>
       </c>
     </row>
@@ -2859,7 +3125,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>("이 구역 방어선은 뚫린 적 없다. 우리가 있는 한.","오염체가 몰려와도 여기서 막는다. 걱정 마쇼.")</t>
+          <t>("이 구역 방어선은 뚫린 적 없다. 우리가 있는 한.","오염체가 몰려와도 여기서 막는다. 걱정 마쇼.","반응로 방어 교대 인원이 부족하오. 시간 되면 한 타임만 서 주시오.")</t>
         </is>
       </c>
     </row>
@@ -3045,8 +3311,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -3055,7 +3321,7 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="39" customWidth="1" min="8" max="8"/>
+    <col width="55" bestFit="1" customWidth="1" min="8" max="8"/>
     <col width="80" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -3142,8 +3408,6 @@
           <t>99</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3181,8 +3445,6 @@
           <t>99</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3220,8 +3482,6 @@
           <t>99</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3259,8 +3519,6 @@
           <t>99</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3298,8 +3556,6 @@
           <t>99</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3337,8 +3593,6 @@
           <t>99</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3376,8 +3630,6 @@
           <t>99</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3415,8 +3667,6 @@
           <t>99</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3456,7 +3706,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>/Game/Data/Weapon/DA_Rifle.DA_Rifle</t>
+          <t>/Game/Data/Primary/Weapons/DA_Rifle.DA_Rifle</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -3503,7 +3753,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>/Game/Data/Weapon/DA_Sniper.DA_Sniper</t>
+          <t>/Game/Data/Primary/Weapons/DA_Sniper.DA_Sniper</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3515,83 +3765,159 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cons_Repair_01</t>
+          <t>Wpn_Shotgun_01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>나노 수리킷</t>
+          <t>브리처 산탄포 MK-II</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>현장에서 외골격을 즉시 복구하는 일회용 키트.</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>/Game/UI/OutUI/Inventory/Icons/T_Cons_Repair_01.T_Cons_Repair_01</t>
+          <t>근거리에서 다수의 산탄을 퍼부어 적진을 돌파하는 전투 산탄포.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>/Game/Data/Primary/Weapons/DA_ShotGun.DA_ShotGun</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>(MinDamage=85,MaxDamage=115,FireRate=0.75,MagazineSize=10,ReloadTime=2.6,Penetration=1.5,CriticalChance=0.1,CriticalMultiplier=1.8,WeakpointMultiplier=1.3,MultiHitMultiplier=8,StatusEffectChance=0.08,BreakPower=35,HipFireAccuracy=0.8,AdsAccuracy=0.65,EffectiveRange=1500,MaxRange=4000,DamageFalloffPercent=0.75,MoveSpeed=560,MoveSpeedWhileFiring=320,MoveSpeedWhileAiming=300,SprintSpeed=840)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Wpn_Bazooka_01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>시즈브레이커 로켓포</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>중장갑 표적과 밀집 진형을 폭발로 분쇄하는 대전차 로켓포.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>/Game/Data/Primary/Weapons/DA_Bazooka.DA_Bazooka</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>(MinDamage=180,MaxDamage=240,FireRate=1,MagazineSize=1,ReloadTime=3.5,Penetration=4,CriticalChance=0.05,CriticalMultiplier=2,WeakpointMultiplier=1.2,MultiHitMultiplier=1,StatusEffectChance=0.15,BreakPower=80,HipFireAccuracy=0.45,AdsAccuracy=0.85,EffectiveRange=6000,MaxRange=10000,DamageFalloffPercent=0.2,MoveSpeed=450,MoveSpeedWhileFiring=180,MoveSpeedWhileAiming=220,SprintSpeed=700)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Cons_Repair_01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>나노 수리킷</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>현장에서 외골격을 즉시 복구하는 일회용 키트.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>/Game/UI/OutUI/Inventory/Icons/T_Cons_Repair_01.T_Cons_Repair_01</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>Mat_Core_01</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>정제 코어</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>모듈 제작과 강화에 쓰이는 정제된 에너지 코어.</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>/Game/UI/OutUI/Inventory/Icons/T_Mat_Core_01.T_Mat_Core_01</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I13"/>
+  <autoFilter ref="A1:I15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3603,7 +3929,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -3667,7 +3993,6 @@
           <t>단발 고관통 레일건. 장갑을 무시하고 꿰뚫는다.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Legendary</t>
@@ -3700,7 +4025,6 @@
           <t>전설급 방어 시스템. 방어력과 체력을 대폭 강화.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Legendary</t>
@@ -3733,7 +4057,6 @@
           <t>방어 한계를 풀어 공격력을 폭증시키나 체력을 깎는다.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Epic</t>
@@ -3766,7 +4089,6 @@
           <t>경량화 구동계. 이동 속도와 스태미나를 함께 강화.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Rare</t>
@@ -3799,7 +4121,6 @@
           <t>에너지 순환을 개선해 최대 스태미나를 늘린다.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Common</t>
@@ -3828,8 +4149,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
@@ -3885,28 +4206,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>지휘관 이준혁</t>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Gate_Arrival_SpeakerName", "모듈 관리관 세라")</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(R=0.2,G=0.8,B=1.0,A=1.0)</t>
+          <t>(R=0.900000,G=0.600000,B=1.000000,A=1.000000)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>화물 이송구역 진입 확인. 장벽이 내려왔다. 적을 전부 정리해야 다음 통로가 열릴 거다.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Gate_Arrival_DialogueText", "화물 구역 진입 확인. 장벽 내려간 거 보이죠? 저거, 우리 시스템이 내린 게 아니에요.")</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.030000</t>
         </is>
       </c>
     </row>
@@ -3918,28 +4241,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>연구원 윤하나</t>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Gate_Encounter_SpeakerName", "모듈 관리관 세라")</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(R=0.9,G=0.6,B=1.0,A=1.0)</t>
+          <t>(R=0.900000,G=0.600000,B=1.000000,A=1.000000)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>전이 반응이 계속 잡혀요. 한 번이 아니에요. 세 차례에 걸쳐 몰려올 거예요. 포위되지 않게 조심하세요.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Gate_Encounter_DialogueText", "반응이 셋으로 갈라져요. 순차로 몰아올 거예요. 한 번에 오는 편이 차라리 나았을 텐데.")</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.030000</t>
         </is>
       </c>
     </row>
@@ -3951,28 +4276,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>지휘관 이준혁</t>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Gate_Clear_SpeakerName", "기갑 장교 발렌")</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>(R=0.2,G=0.8,B=1.0,A=1.0)</t>
+          <t>(R=0.200000,G=0.800000,B=1.000000,A=1.000000)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>좋아, 장벽이 풀렸다. 다음은 동력 제어구역이다. 리액터부터 확보해.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Gate_Clear_DialogueText", "장벽 해제 확인. 다음은 동력 구역이다. 세라, 반응로 상태는.")</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.030000</t>
         </is>
       </c>
     </row>
@@ -3984,28 +4311,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>방벽 AI 세라</t>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_System_Alert_SpeakerName", "기갑 장교 발렌")</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>(R=1.0,G=0.85,B=0.0,A=1.0)</t>
+          <t>(R=0.200000,G=0.800000,B=1.000000,A=1.000000)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>긴급 작전입니다. 화물 이송구역을 돌파하고 동력 제어구역의 리액터를 확보하세요. 균열 중심의 대형 개체까지 제거해야 합니다.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_System_Alert_DialogueText", "균열이 궤도 엘리베이터 하부를 삼켰다. 우리가 오염이라 부르던 건 전부 저 아래서 올라온 거였어. 저기가 막히면 지상 보급은 끝이다. 화물 구역을 뚫고 반응로를 확보한다.")</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.030000</t>
         </is>
       </c>
     </row>
@@ -4017,28 +4346,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>연구원 윤하나</t>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_MidBrief_SpeakerName", "모듈 관리관 세라")</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>(R=0.9,G=0.6,B=1.0,A=1.0)</t>
+          <t>(R=0.900000,G=0.600000,B=1.000000,A=1.000000)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>적들이 리액터로 몰려들고 있어요! 원거리형도 보여요. 세 번의 공세만 버티면 돼요. 리액터를 지켜 주세요.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_MidBrief_DialogueText", "반응로 온도가 올라가요. 저것들, 부수려는 게 아니에요. 켜려는 거예요. 세 차례만 막아 주세요.")</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.030000</t>
         </is>
       </c>
     </row>
@@ -4050,28 +4381,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>지휘관 이준혁</t>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Boss_Approach_SpeakerName", "모듈 관리관 세라")</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>(R=0.2,G=0.8,B=1.0,A=1.0)</t>
+          <t>(R=0.900000,G=0.600000,B=1.000000,A=1.000000)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>핵심부에 대형 반응이 나타났다. 중장갑 메카다. 놈이 적들을 불러들이고 있다. 여기서 끝내라.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Boss_Approach_DialogueText", "대형 개체 신호 포착. 균열에서 나온 게 아니에요. 우리 규격이에요. 3주 전 실종된 기체.")</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.030000</t>
         </is>
       </c>
     </row>
@@ -4083,28 +4416,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>연구원 윤하나</t>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Boss_Clear_SpeakerName", "모듈 관리관 세라")</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>(R=0.9,G=0.6,B=1.0,A=1.0)</t>
+          <t>(R=0.900000,G=0.600000,B=1.000000,A=1.000000)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대형 개체 반응 소멸! 주변의 전이 신호도 전부 꺼지고 있어요. 해냈어요!</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Boss_Clear_DialogueText", "신호 소멸. 식별 코드까지 같이 지워졌어요. 이건 보고서에 어떻게 쓰죠.")</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.030000</t>
         </is>
       </c>
     </row>
@@ -4116,28 +4451,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>지휘관 이준혁</t>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Dungeon_Complete_SpeakerName", "기갑 장교 발렌")</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>(R=0.2,G=0.8,B=1.0,A=1.0)</t>
+          <t>(R=0.200000,G=0.800000,B=1.000000,A=1.000000)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>전 구역 안정화 확인. 궤도 엘리베이터를 확보했다. 수고했다. 이제 복귀해.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Dungeon_Complete_DialogueText", "전 구역 안정화. 궤도 접근로는 확보했다. 수고했다. 대형 개체 항목은 비워 둬라. 그건 내가 처리한다.")</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.030000</t>
         </is>
       </c>
     </row>
@@ -4149,33 +4486,842 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>방벽 AI 세라</t>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Base_Welcome_SpeakerName", "관제 AI 아르케")</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>(R=1.0,G=0.85,B=0.0,A=1.0)</t>
+          <t>(R=1.000000,G=0.850000,B=0.000000,A=1.000000)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>전초기지 복귀를 환영합니다. 보급창고에서 장비와 소모품을 점검한 뒤 출격을 준비해 주세요.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Base_Welcome_DialogueText", "귀환 기록 갱신. 외골격 동기율 71퍼센트, 권장치 미만입니다. 창구부터 들르시죠. 이번엔 돌아오셨으니까요.")</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.030000</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Radio_Depot_Arrive</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Depot_Arrive_SpeakerName", "교육 조교 탈")</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>(R=0.550000,G=0.900000,B=0.600000,A=1.000000)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Depot_Arrive_DialogueText", "거기 서서 아래를 봐. 3주 전엔 저 구역까지 우리 방어선이었다. 지금은 네가 선 자리까지 밀렸고. …네가 실종 처리된 것도 그날이야. 정찰은 이래서 하는 거다.")</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.030000</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Radio_Hunt_Start</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Hunt_Start_SpeakerName", "기갑 장교 발렌")</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>(R=0.200000,G=0.800000,B=1.000000,A=1.000000)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Hunt_Start_DialogueText", "목표는 궤도 엘리베이터다. 쏟아지는 적들을 뚫고 균열을 돌파해라.")</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.030000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Radio_Hunt_Clear</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Hunt_Clear_SpeakerName", "기갑 장교 발렌")</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>(R=0.200000,G=0.800000,B=1.000000,A=1.000000)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Hunt_Clear_DialogueText", "셋 정리 확인. 그런데 접근 신호는 넷이었다. 나머지 하나는 교전 없이 빠졌어. 돌격형이 물러서는 건 처음 본다. 보고하러 와라.")</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.030000</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Radio_Boss_Warning</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Boss_Warning_SpeakerName", "기갑 장교 발렌")</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>(R=0.200000,G=0.800000,B=1.000000,A=1.000000)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Boss_Warning_DialogueText", "들었지. 저건 이제 우리 쪽이 아니다. 끝내라.")</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.030000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Radio_Welcome_Start</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Welcome_Start_SpeakerName", "교육 조교 탈")</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>(R=0.550000,G=0.900000,B=0.600000,A=1.000000)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Welcome_Start_DialogueText", "복귀 확인. 생존 기록은 갱신했다. 이제 데크에게 가서 복귀 보급을 수령해.")</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.030000</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Radio_Welcome_Clear</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Welcome_Clear_SpeakerName", "보급상 데크")</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>(R=1.000000,G=0.650000,B=0.250000,A=1.000000)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Welcome_Clear_DialogueText", "생존 신고하러 왔나? 탈 쪽 확인은 넘어왔어. 돌아왔으니 네 몫은 챙겨야지. 여기, 복귀 보급품 받아.")</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.030000</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Radio_Mobility_Start</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Mobility_Start_SpeakerName", "모듈 관리관 세라")</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>(R=0.900000,G=0.600000,B=1.000000,A=1.000000)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Mobility_Start_DialogueText", "차기 편성은 전부 고속 강습이에요. 지금 구동계로는 진입 전에 낙오해요. 데크한테 질풍 모듈부터 받아 오세요.")</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.030000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Radio_Mobility_Clear</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Mobility_Clear_SpeakerName", "모듈 관리관 세라")</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>(R=0.900000,G=0.600000,B=1.000000,A=1.000000)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Mobility_Clear_DialogueText", "체결 완료. 동기율 3퍼센트 올랐어요. …3주 전에도 이 수치였으면 좋았을 텐데요.")</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.030000</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Radio_Endurance_Start</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Endurance_Start_SpeakerName", "정비병 보로스")</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>(R=0.700000,G=0.750000,B=0.800000,A=1.000000)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Endurance_Start_DialogueText", "장기 침투는 화력이 아니라 순환이 버텨야 한다. 지구력 코어 물어다 와. 내가 뼈대에 물려 주지.")</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0.030000</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Radio_Endurance_Clear</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Endurance_Clear_SpeakerName", "정비병 보로스")</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>(R=0.700000,G=0.750000,B=0.800000,A=1.000000)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Endurance_Clear_DialogueText", "에너지 순환 정상. 이제 오래 뛸 수 있다. 오래 뛴다는 건 오래 살아 있다는 뜻이야.")</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0.030000</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Radio_Arsenal_Clear</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Arsenal_Clear_SpeakerName", "모듈 관리관 세라")</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>(R=0.900000,G=0.600000,B=1.000000,A=1.000000)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Arsenal_Clear_DialogueText", "광폭 회로 체결했어요. 방어 한계를 푸는 물건이니까, 쓰는 만큼 깎여 나가는 것도 잊지 마세요.")</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0.030000</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Radio_Fortress_Clear</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Fortress_Clear_SpeakerName", "모듈 관리관 세라")</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>(R=0.900000,G=0.600000,B=1.000000,A=1.000000)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Fortress_Clear_DialogueText", "철벽 프로토콜, 정상 작동. 이거 하나면 반응로 앞에서 한참은 버팁니다. 그 뒤는 장담 못 해요.")</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0.030000</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Radio_Apex_Clear</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Apex_Clear_SpeakerName", "보급상 데크")</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>(R=1.000000,G=0.650000,B=0.250000,A=1.000000)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Apex_Clear_DialogueText", "관통자, 인수 확인했다. 장갑 무시하는 물건이야. 값어치는 하겠지 — 그쪽이 살아 오면.")</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0.030000</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Radio_Shooter_Start</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Shooter_Start_SpeakerName", "기갑병 릭")</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>(R=0.950000,G=0.550000,B=0.400000,A=1.000000)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Shooter_Start_DialogueText", "사격형은 엄폐 뒤에서 진입로만 재고 있습니다. 머리 내밀면 그때 옵니다. 측면으로 붙으십쇼.")</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0.030000</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Radio_Shooter_Clear</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Shooter_Clear_SpeakerName", "기갑병 릭")</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>(R=0.950000,G=0.550000,B=0.400000,A=1.000000)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Shooter_Clear_DialogueText", "진입로 열렸습니다. …저것들 사격선이 우리 교범이랑 똑같던데. 기분 탓이겠죠.")</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0.030000</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Radio_Reach_Clear</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Reach_Clear_SpeakerName", "보초병 콜")</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>(R=0.600000,G=0.800000,B=0.900000,A=1.000000)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Reach_Clear_DialogueText", "정찰 결과 접수했습니다. 이 초소도 다음 주면 뒤로 물린다더군요. 조심히 돌아가십시오.")</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0.030000</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Radio_Talk_Clear</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Talk_Clear_SpeakerName", "기갑 장교 발렌")</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>(R=0.200000,G=0.800000,B=1.000000,A=1.000000)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Talk_Clear_DialogueText", "보고 확인. 교전 기록은 내가 정리한다. …신호 없던 넷째 건은 네 보고서에서 빼 두지.")</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0.030000</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Radio_Reactor_Hold</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Reactor_Hold_SpeakerName", "모듈 관리관 세라")</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>(R=0.900000,G=0.600000,B=1.000000,A=1.000000)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Reactor_Hold_DialogueText", "세 차례 다 막았어요. 온도 하강 중… 잠깐, 점화 시퀀스가 아직 살아 있어요. 누가 밖에서 붙잡고 있어요.")</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0.030000</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Radio_Defend_Start</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Defend_Start_SpeakerName", "기갑병 보드")</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>(R=0.950000,G=0.550000,B=0.400000,A=1.000000)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Defend_Start_DialogueText", "반응로 방어선, 지금부터 계승자님 기준으로 잡습니다. 저게 터지면 이 구역은 지도에서 지워집니다.")</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0.030000</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Radio_Defend_Clear</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Defend_Clear_SpeakerName", "기갑병 보드")</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>(R=0.950000,G=0.550000,B=0.400000,A=1.000000)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Defend_Clear_DialogueText", "방어 성공. 반응로 무사합니다. 우리 방어선은 아직 안 뚫렸습니다 — 계승자님 덕에요.")</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0.030000</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Radio_Capture_Start</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Capture_Start_SpeakerName", "보초병 렌")</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>(R=0.600000,G=0.800000,B=0.900000,A=1.000000)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Capture_Start_DialogueText", "전초기지 점령 지원합니다. 구역 안에 계속 계셔야 해요. 한 발만 벗어나도 계기가 처음으로 돌아갑니다.")</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0.030000</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Radio_Capture_Clear</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Capture_Clear_SpeakerName", "보초병 렌")</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>(R=0.600000,G=0.800000,B=0.900000,A=1.000000)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("DT_RadioTransmission [73FCC5C79BC4DB384C54AB86C65E1510]", "Radio_Capture_Clear_DialogueText", "점령 완료. 깃발 올렸습니다. …근무 중 잡담은 금지지만, 이건 보고할 맛이 나네요.")</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>0.030000</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Radio_Elevator_Move</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("", "", "기갑 장교 발렌")</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>(R=0.200000,G=0.800000,B=1.000000,A=1.000000)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NSLOCTEXT("", "", "전송 게이트가 개방되었다. 즉시 궤도 엘리베이터로 이동해 돌파하라.")</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0.030000</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:G16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>